--- a/artfynd/A 46889-2024 artfynd.xlsx
+++ b/artfynd/A 46889-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152510</v>
+        <v>121152460</v>
       </c>
       <c r="B2" t="n">
-        <v>91988</v>
+        <v>97041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3100</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800099</v>
+        <v>800408</v>
       </c>
       <c r="R2" t="n">
-        <v>7412370</v>
+        <v>7412340</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152460</v>
+        <v>121152510</v>
       </c>
       <c r="B3" t="n">
-        <v>97031</v>
+        <v>91998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800408</v>
+        <v>800099</v>
       </c>
       <c r="R3" t="n">
-        <v>7412340</v>
+        <v>7412370</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 46889-2024 artfynd.xlsx
+++ b/artfynd/A 46889-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152460</v>
+        <v>121152510</v>
       </c>
       <c r="B2" t="n">
-        <v>97041</v>
+        <v>91998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800408</v>
+        <v>800099</v>
       </c>
       <c r="R2" t="n">
-        <v>7412340</v>
+        <v>7412370</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152510</v>
+        <v>121152460</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>97041</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800099</v>
+        <v>800408</v>
       </c>
       <c r="R3" t="n">
-        <v>7412370</v>
+        <v>7412340</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 46889-2024 artfynd.xlsx
+++ b/artfynd/A 46889-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152510</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121152460</v>
       </c>
       <c r="B3" t="n">
-        <v>97041</v>
+        <v>97054</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 46889-2024 artfynd.xlsx
+++ b/artfynd/A 46889-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152510</v>
       </c>
       <c r="B2" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121152460</v>
       </c>
       <c r="B3" t="n">
-        <v>97054</v>
+        <v>97055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 46889-2024 artfynd.xlsx
+++ b/artfynd/A 46889-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152510</v>
       </c>
       <c r="B2" t="n">
-        <v>92011</v>
+        <v>92014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121152460</v>
       </c>
       <c r="B3" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 46889-2024 artfynd.xlsx
+++ b/artfynd/A 46889-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152510</v>
+        <v>121152460</v>
       </c>
       <c r="B2" t="n">
-        <v>92014</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3100</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800099</v>
+        <v>800408</v>
       </c>
       <c r="R2" t="n">
-        <v>7412370</v>
+        <v>7412340</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152460</v>
+        <v>121152510</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>92014</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800408</v>
+        <v>800099</v>
       </c>
       <c r="R3" t="n">
-        <v>7412340</v>
+        <v>7412370</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
